--- a/data/nzd0525/nzd0525.xlsx
+++ b/data/nzd0525/nzd0525.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G470"/>
+  <dimension ref="A1:G472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13124,6 +13124,60 @@
         <v>357.69</v>
       </c>
       <c r="G470" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>370.14</v>
+      </c>
+      <c r="C471" t="n">
+        <v>368.14</v>
+      </c>
+      <c r="D471" t="n">
+        <v>365.93</v>
+      </c>
+      <c r="E471" t="n">
+        <v>363.72</v>
+      </c>
+      <c r="F471" t="n">
+        <v>357.81</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>370.62</v>
+      </c>
+      <c r="C472" t="n">
+        <v>368.07</v>
+      </c>
+      <c r="D472" t="n">
+        <v>365.98</v>
+      </c>
+      <c r="E472" t="n">
+        <v>363.74</v>
+      </c>
+      <c r="F472" t="n">
+        <v>357.42</v>
+      </c>
+      <c r="G472" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13140,7 +13194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B504"/>
+  <dimension ref="A1:B506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18183,6 +18237,26 @@
       </c>
       <c r="B504" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>-0.48</v>
       </c>
     </row>
   </sheetData>
@@ -18351,28 +18425,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.847009672084363</v>
+        <v>2.841267280788428</v>
       </c>
       <c r="J2" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K2" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8263401789523031</v>
+        <v>0.8269307587058379</v>
       </c>
       <c r="M2" t="n">
-        <v>8.033251562742882</v>
+        <v>8.027593706914082</v>
       </c>
       <c r="N2" t="n">
-        <v>93.8801861708737</v>
+        <v>93.66203346816221</v>
       </c>
       <c r="O2" t="n">
-        <v>9.689178818190616</v>
+        <v>9.677914727262387</v>
       </c>
       <c r="P2" t="n">
-        <v>301.9521327696411</v>
+        <v>302.0099290495301</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18429,28 +18503,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.012719859764279</v>
+        <v>3.005330172486131</v>
       </c>
       <c r="J3" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K3" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L3" t="n">
-        <v>0.814812498123071</v>
+        <v>0.8151958045198573</v>
       </c>
       <c r="M3" t="n">
-        <v>8.708861214333348</v>
+        <v>8.706641182627713</v>
       </c>
       <c r="N3" t="n">
-        <v>113.6912574075834</v>
+        <v>113.5070749968734</v>
       </c>
       <c r="O3" t="n">
-        <v>10.66261025300951</v>
+        <v>10.65396991721271</v>
       </c>
       <c r="P3" t="n">
-        <v>297.1916922260074</v>
+        <v>297.266069643998</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18507,28 +18581,28 @@
         <v>0.196</v>
       </c>
       <c r="I4" t="n">
-        <v>3.004036024668249</v>
+        <v>2.996882496523798</v>
       </c>
       <c r="J4" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K4" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8408162355146687</v>
+        <v>0.8411280114444935</v>
       </c>
       <c r="M4" t="n">
-        <v>7.870249816094304</v>
+        <v>7.871147566343117</v>
       </c>
       <c r="N4" t="n">
-        <v>94.340137937443</v>
+        <v>94.2192028169311</v>
       </c>
       <c r="O4" t="n">
-        <v>9.712885150018145</v>
+        <v>9.706657654256233</v>
       </c>
       <c r="P4" t="n">
-        <v>295.005218258862</v>
+        <v>295.0771734781875</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18585,28 +18659,28 @@
         <v>0.199</v>
       </c>
       <c r="I5" t="n">
-        <v>2.731331601871581</v>
+        <v>2.725933248468571</v>
       </c>
       <c r="J5" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K5" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8387796504853093</v>
+        <v>0.839334443162319</v>
       </c>
       <c r="M5" t="n">
-        <v>7.215620278417981</v>
+        <v>7.212467276989352</v>
       </c>
       <c r="N5" t="n">
-        <v>79.02716631727554</v>
+        <v>78.85093191273388</v>
       </c>
       <c r="O5" t="n">
-        <v>8.889722510701644</v>
+        <v>8.879804722668956</v>
       </c>
       <c r="P5" t="n">
-        <v>297.9557740803783</v>
+        <v>298.0101085523578</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18663,28 +18737,28 @@
         <v>0.1438</v>
       </c>
       <c r="I6" t="n">
-        <v>1.847895139294768</v>
+        <v>1.841953529001423</v>
       </c>
       <c r="J6" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K6" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7577056699994238</v>
+        <v>0.7577842075643135</v>
       </c>
       <c r="M6" t="n">
-        <v>6.329204517515721</v>
+        <v>6.330910150452359</v>
       </c>
       <c r="N6" t="n">
-        <v>60.18010456482355</v>
+        <v>60.11777549839358</v>
       </c>
       <c r="O6" t="n">
-        <v>7.757583680813475</v>
+        <v>7.753565341079779</v>
       </c>
       <c r="P6" t="n">
-        <v>315.7298635305924</v>
+        <v>315.7896666933784</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18722,7 +18796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G470"/>
+  <dimension ref="A1:G472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36111,6 +36185,80 @@
         </is>
       </c>
     </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>-46.293701140219895,169.92599264878544</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>-46.29429290285237,169.92572265887364</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>-46.2948840956902,169.92545006774554</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-46.295475281919224,169.9251774760768</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-46.29605653838198,169.92485906065676</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>-46.29370242750177,169.925998593187</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>-46.2942927151221,169.92572179197327</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>-46.294884229784444,169.92545068696617</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-46.2954753355574,169.92517772376746</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-46.29605549242648,169.92485423064366</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0525/nzd0525.xlsx
+++ b/data/nzd0525/nzd0525.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G472"/>
+  <dimension ref="A1:G473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13180,6 +13180,33 @@
       <c r="G472" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>370.39</v>
+      </c>
+      <c r="C473" t="n">
+        <v>368.24</v>
+      </c>
+      <c r="D473" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="E473" t="n">
+        <v>363.76</v>
+      </c>
+      <c r="F473" t="n">
+        <v>358.25</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B506"/>
+  <dimension ref="A1:B507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18257,6 +18284,16 @@
       </c>
       <c r="B506" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -18425,28 +18462,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.841267280788428</v>
+        <v>2.83838293414397</v>
       </c>
       <c r="J2" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K2" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8269307587058379</v>
+        <v>0.8272175664012856</v>
       </c>
       <c r="M2" t="n">
-        <v>8.027593706914082</v>
+        <v>8.024807630945345</v>
       </c>
       <c r="N2" t="n">
-        <v>93.66203346816221</v>
+        <v>93.55551078421028</v>
       </c>
       <c r="O2" t="n">
-        <v>9.677914727262387</v>
+        <v>9.672409771313987</v>
       </c>
       <c r="P2" t="n">
-        <v>302.0099290495301</v>
+        <v>302.0390234363662</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18503,28 +18540,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.005330172486131</v>
+        <v>3.001686910611061</v>
       </c>
       <c r="J3" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K3" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8151958045198573</v>
+        <v>0.8153915366682181</v>
       </c>
       <c r="M3" t="n">
-        <v>8.706641182627713</v>
+        <v>8.705243107735836</v>
       </c>
       <c r="N3" t="n">
-        <v>113.5070749968734</v>
+        <v>113.4132387247964</v>
       </c>
       <c r="O3" t="n">
-        <v>10.65396991721271</v>
+        <v>10.64956518947118</v>
       </c>
       <c r="P3" t="n">
-        <v>297.266069643998</v>
+        <v>297.3028192040907</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18581,28 +18618,28 @@
         <v>0.196</v>
       </c>
       <c r="I4" t="n">
-        <v>2.996882496523798</v>
+        <v>2.99336079363612</v>
       </c>
       <c r="J4" t="n">
+        <v>472</v>
+      </c>
+      <c r="K4" t="n">
         <v>471</v>
       </c>
-      <c r="K4" t="n">
-        <v>470</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.8411280114444935</v>
+        <v>0.8412889105081849</v>
       </c>
       <c r="M4" t="n">
-        <v>7.871147566343117</v>
+        <v>7.87125570389352</v>
       </c>
       <c r="N4" t="n">
-        <v>94.2192028169311</v>
+        <v>94.15653699184902</v>
       </c>
       <c r="O4" t="n">
-        <v>9.706657654256233</v>
+        <v>9.703429135715323</v>
       </c>
       <c r="P4" t="n">
-        <v>295.0771734781875</v>
+        <v>295.1126749243006</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18659,28 +18696,28 @@
         <v>0.199</v>
       </c>
       <c r="I5" t="n">
-        <v>2.725933248468571</v>
+        <v>2.723230780550116</v>
       </c>
       <c r="J5" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K5" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L5" t="n">
-        <v>0.839334443162319</v>
+        <v>0.8396054344611618</v>
       </c>
       <c r="M5" t="n">
-        <v>7.212467276989352</v>
+        <v>7.210859865839446</v>
       </c>
       <c r="N5" t="n">
-        <v>78.85093191273388</v>
+        <v>78.76456249853599</v>
       </c>
       <c r="O5" t="n">
-        <v>8.879804722668956</v>
+        <v>8.874940140560723</v>
       </c>
       <c r="P5" t="n">
-        <v>298.0101085523578</v>
+        <v>298.037368329605</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18737,28 +18774,28 @@
         <v>0.1438</v>
       </c>
       <c r="I6" t="n">
-        <v>1.841953529001423</v>
+        <v>1.8392694811488</v>
       </c>
       <c r="J6" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K6" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7577842075643135</v>
+        <v>0.7579268488411486</v>
       </c>
       <c r="M6" t="n">
-        <v>6.330910150452359</v>
+        <v>6.330410048428503</v>
       </c>
       <c r="N6" t="n">
-        <v>60.11777549839358</v>
+        <v>60.06999878686396</v>
       </c>
       <c r="O6" t="n">
-        <v>7.753565341079779</v>
+        <v>7.750483777601496</v>
       </c>
       <c r="P6" t="n">
-        <v>315.7896666933784</v>
+        <v>315.816740667535</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18796,7 +18833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G472"/>
+  <dimension ref="A1:G473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36259,6 +36296,43 @@
         </is>
       </c>
     </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>-46.29370181067924,169.92599574482787</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>-46.294293171038454,169.9257238973027</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>-46.29488455161059,169.92545217309558</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-46.29547538919556,169.9251779714581</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-46.29605771843408,169.9248645099025</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0525/nzd0525.xlsx
+++ b/data/nzd0525/nzd0525.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G473"/>
+  <dimension ref="A1:G474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13207,6 +13207,33 @@
       <c r="G473" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>369.78</v>
+      </c>
+      <c r="C474" t="n">
+        <v>364.55</v>
+      </c>
+      <c r="D474" t="n">
+        <v>361.07</v>
+      </c>
+      <c r="E474" t="n">
+        <v>358.1</v>
+      </c>
+      <c r="F474" t="n">
+        <v>354.03</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13221,7 +13248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B507"/>
+  <dimension ref="A1:B508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18294,6 +18321,16 @@
       </c>
       <c r="B507" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -18462,28 +18499,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.83838293414397</v>
+        <v>2.835005458707494</v>
       </c>
       <c r="J2" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K2" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8272175664012856</v>
+        <v>0.8274209119535257</v>
       </c>
       <c r="M2" t="n">
-        <v>8.024807630945345</v>
+        <v>8.024431695199008</v>
       </c>
       <c r="N2" t="n">
-        <v>93.55551078421028</v>
+        <v>93.48142859642043</v>
       </c>
       <c r="O2" t="n">
-        <v>9.672409771313987</v>
+        <v>9.668579450799401</v>
       </c>
       <c r="P2" t="n">
-        <v>302.0390234363662</v>
+        <v>302.073342976382</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18540,28 +18577,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.001686910611061</v>
+        <v>2.996184530626817</v>
       </c>
       <c r="J3" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K3" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8153915366682181</v>
+        <v>0.8151750302596552</v>
       </c>
       <c r="M3" t="n">
-        <v>8.705243107735836</v>
+        <v>8.712139632826723</v>
       </c>
       <c r="N3" t="n">
-        <v>113.4132387247964</v>
+        <v>113.5018016625062</v>
       </c>
       <c r="O3" t="n">
-        <v>10.64956518947118</v>
+        <v>10.65372243220679</v>
       </c>
       <c r="P3" t="n">
-        <v>297.3028192040907</v>
+        <v>297.3587305359725</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18618,28 +18655,28 @@
         <v>0.196</v>
       </c>
       <c r="I4" t="n">
-        <v>2.99336079363612</v>
+        <v>2.987387086955514</v>
       </c>
       <c r="J4" t="n">
+        <v>473</v>
+      </c>
+      <c r="K4" t="n">
         <v>472</v>
       </c>
-      <c r="K4" t="n">
-        <v>471</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.8412889105081849</v>
+        <v>0.840889176569982</v>
       </c>
       <c r="M4" t="n">
-        <v>7.87125570389352</v>
+        <v>7.882790739526661</v>
       </c>
       <c r="N4" t="n">
-        <v>94.15653699184902</v>
+        <v>94.34503867929909</v>
       </c>
       <c r="O4" t="n">
-        <v>9.703429135715323</v>
+        <v>9.71313742718073</v>
       </c>
       <c r="P4" t="n">
-        <v>295.1126749243006</v>
+        <v>295.17333955705</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18696,28 +18733,28 @@
         <v>0.199</v>
       </c>
       <c r="I5" t="n">
-        <v>2.723230780550116</v>
+        <v>2.717819939297831</v>
       </c>
       <c r="J5" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K5" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8396054344611618</v>
+        <v>0.8392171622607263</v>
       </c>
       <c r="M5" t="n">
-        <v>7.210859865839446</v>
+        <v>7.222723526562074</v>
       </c>
       <c r="N5" t="n">
-        <v>78.76456249853599</v>
+        <v>78.91554475115736</v>
       </c>
       <c r="O5" t="n">
-        <v>8.874940140560723</v>
+        <v>8.883442167941284</v>
       </c>
       <c r="P5" t="n">
-        <v>298.037368329605</v>
+        <v>298.0923495090006</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18774,28 +18811,28 @@
         <v>0.1438</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8392694811488</v>
+        <v>1.834580815141661</v>
       </c>
       <c r="J6" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K6" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7579268488411486</v>
+        <v>0.7572022434149899</v>
       </c>
       <c r="M6" t="n">
-        <v>6.330410048428503</v>
+        <v>6.339503272782923</v>
       </c>
       <c r="N6" t="n">
-        <v>60.06999878686396</v>
+        <v>60.18140711314383</v>
       </c>
       <c r="O6" t="n">
-        <v>7.750483777601496</v>
+        <v>7.757667633583165</v>
       </c>
       <c r="P6" t="n">
-        <v>315.816740667535</v>
+        <v>315.8643836078552</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18833,7 +18870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G473"/>
+  <dimension ref="A1:G474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36333,6 +36370,43 @@
         </is>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>-46.29370017475828,169.92598819048447</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>-46.294283274962986,169.9256781992777</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>-46.29487106171522,169.925389879519</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-46.29546020957359,169.92510787502223</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-46.29604640065116,169.924812246692</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0525/nzd0525.xlsx
+++ b/data/nzd0525/nzd0525.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G474"/>
+  <dimension ref="A1:G476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13234,6 +13234,60 @@
       <c r="G474" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>371.83</v>
+      </c>
+      <c r="C475" t="n">
+        <v>364.74</v>
+      </c>
+      <c r="D475" t="n">
+        <v>360.83</v>
+      </c>
+      <c r="E475" t="n">
+        <v>356.33</v>
+      </c>
+      <c r="F475" t="n">
+        <v>353.48</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>370.81</v>
+      </c>
+      <c r="C476" t="n">
+        <v>364.1</v>
+      </c>
+      <c r="D476" t="n">
+        <v>359.39</v>
+      </c>
+      <c r="E476" t="n">
+        <v>354.66</v>
+      </c>
+      <c r="F476" t="n">
+        <v>352.56</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B508"/>
+  <dimension ref="A1:B510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18331,6 +18385,26 @@
       </c>
       <c r="B508" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -18499,28 +18573,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.835005458707494</v>
+        <v>2.829540585060492</v>
       </c>
       <c r="J2" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K2" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8274209119535257</v>
+        <v>0.8280775104256148</v>
       </c>
       <c r="M2" t="n">
-        <v>8.024431695199008</v>
+        <v>8.017245514775549</v>
       </c>
       <c r="N2" t="n">
-        <v>93.48142859642043</v>
+        <v>93.2521161681414</v>
       </c>
       <c r="O2" t="n">
-        <v>9.668579450799401</v>
+        <v>9.656713528325328</v>
       </c>
       <c r="P2" t="n">
-        <v>302.073342976382</v>
+        <v>302.1290222451738</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18577,28 +18651,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.996184530626817</v>
+        <v>2.985072273602296</v>
       </c>
       <c r="J3" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K3" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8151750302596552</v>
+        <v>0.8146994753344708</v>
       </c>
       <c r="M3" t="n">
-        <v>8.712139632826723</v>
+        <v>8.726053607533023</v>
       </c>
       <c r="N3" t="n">
-        <v>113.5018016625062</v>
+        <v>113.6983213849807</v>
       </c>
       <c r="O3" t="n">
-        <v>10.65372243220679</v>
+        <v>10.6629414977754</v>
       </c>
       <c r="P3" t="n">
-        <v>297.3587305359725</v>
+        <v>297.4719428232626</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18655,28 +18729,28 @@
         <v>0.196</v>
       </c>
       <c r="I4" t="n">
-        <v>2.987387086955514</v>
+        <v>2.974627326508124</v>
       </c>
       <c r="J4" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K4" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L4" t="n">
-        <v>0.840889176569982</v>
+        <v>0.8398424645928293</v>
       </c>
       <c r="M4" t="n">
-        <v>7.882790739526661</v>
+        <v>7.909500914504713</v>
       </c>
       <c r="N4" t="n">
-        <v>94.34503867929909</v>
+        <v>94.84014512794197</v>
       </c>
       <c r="O4" t="n">
-        <v>9.71313742718073</v>
+        <v>9.738590510332692</v>
       </c>
       <c r="P4" t="n">
-        <v>295.17333955705</v>
+        <v>295.3032633327989</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18733,28 +18807,28 @@
         <v>0.199</v>
       </c>
       <c r="I5" t="n">
-        <v>2.717819939297831</v>
+        <v>2.704749829069891</v>
       </c>
       <c r="J5" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K5" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8392171622607263</v>
+        <v>0.8376938351784059</v>
       </c>
       <c r="M5" t="n">
-        <v>7.222723526562074</v>
+        <v>7.258348014711308</v>
       </c>
       <c r="N5" t="n">
-        <v>78.91554475115736</v>
+        <v>79.51865759459176</v>
       </c>
       <c r="O5" t="n">
-        <v>8.883442167941284</v>
+        <v>8.917323454635463</v>
       </c>
       <c r="P5" t="n">
-        <v>298.0923495090006</v>
+        <v>298.2255117771523</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18811,28 +18885,28 @@
         <v>0.1438</v>
       </c>
       <c r="I6" t="n">
-        <v>1.834580815141661</v>
+        <v>1.824369347972155</v>
       </c>
       <c r="J6" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K6" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7572022434149899</v>
+        <v>0.7552846403474978</v>
       </c>
       <c r="M6" t="n">
-        <v>6.339503272782923</v>
+        <v>6.362002578215335</v>
       </c>
       <c r="N6" t="n">
-        <v>60.18140711314383</v>
+        <v>60.49803224923131</v>
       </c>
       <c r="O6" t="n">
-        <v>7.757667633583165</v>
+        <v>7.778048100213273</v>
       </c>
       <c r="P6" t="n">
-        <v>315.8643836078552</v>
+        <v>315.9684197029789</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18870,7 +18944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G474"/>
+  <dimension ref="A1:G476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36407,6 +36481,80 @@
         </is>
       </c>
     </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>-46.29370567252352,169.9260135780338</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>-46.29428378451743,169.92568055229214</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>-46.29487041806135,169.9253869072617</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>-46.29545546258069,169.92508595441373</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>-46.29604492558294,169.9248054351378</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>-46.29370293705076,169.92600094617933</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>-46.29428206812327,169.925672626349</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>-46.294866556136405,169.92536907371928</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>-46.2954509837757,169.92506527226132</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>-46.29604245819521,169.92479404126618</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0525/nzd0525.xlsx
+++ b/data/nzd0525/nzd0525.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G476"/>
+  <dimension ref="A1:G481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13286,6 +13286,141 @@
         <v>352.56</v>
       </c>
       <c r="G476" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>371.46</v>
+      </c>
+      <c r="C477" t="n">
+        <v>364.39</v>
+      </c>
+      <c r="D477" t="n">
+        <v>359.17</v>
+      </c>
+      <c r="E477" t="n">
+        <v>353.74</v>
+      </c>
+      <c r="F477" t="n">
+        <v>352.72</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="C478" t="n">
+        <v>364.32</v>
+      </c>
+      <c r="D478" t="n">
+        <v>359.04</v>
+      </c>
+      <c r="E478" t="n">
+        <v>354.61</v>
+      </c>
+      <c r="F478" t="n">
+        <v>352.64</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="C479" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="D479" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="E479" t="n">
+        <v>355.6</v>
+      </c>
+      <c r="F479" t="n">
+        <v>352.84</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>372.21</v>
+      </c>
+      <c r="C480" t="n">
+        <v>363.81</v>
+      </c>
+      <c r="D480" t="n">
+        <v>358.89</v>
+      </c>
+      <c r="E480" t="n">
+        <v>354.87</v>
+      </c>
+      <c r="F480" t="n">
+        <v>352.46</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="C481" t="n">
+        <v>363.79</v>
+      </c>
+      <c r="D481" t="n">
+        <v>359.64</v>
+      </c>
+      <c r="E481" t="n">
+        <v>355.82</v>
+      </c>
+      <c r="F481" t="n">
+        <v>354.16</v>
+      </c>
+      <c r="G481" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13302,7 +13437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B510"/>
+  <dimension ref="A1:B515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18405,6 +18540,56 @@
       </c>
       <c r="B510" t="n">
         <v>0.37</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -18573,28 +18758,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.829540585060492</v>
+        <v>2.818063380029312</v>
       </c>
       <c r="J2" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8280775104256148</v>
+        <v>0.8300224990020946</v>
       </c>
       <c r="M2" t="n">
-        <v>8.017245514775549</v>
+        <v>7.988807050739294</v>
       </c>
       <c r="N2" t="n">
-        <v>93.2521161681414</v>
+        <v>92.57849168064435</v>
       </c>
       <c r="O2" t="n">
-        <v>9.656713528325328</v>
+        <v>9.621771753717937</v>
       </c>
       <c r="P2" t="n">
-        <v>302.1290222451738</v>
+        <v>302.2462976233838</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18651,28 +18836,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.985072273602296</v>
+        <v>2.957455351410103</v>
       </c>
       <c r="J3" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K3" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8146994753344708</v>
+        <v>0.8133962821506957</v>
       </c>
       <c r="M3" t="n">
-        <v>8.726053607533023</v>
+        <v>8.760377615772089</v>
       </c>
       <c r="N3" t="n">
-        <v>113.6983213849807</v>
+        <v>114.2250917661656</v>
       </c>
       <c r="O3" t="n">
-        <v>10.6629414977754</v>
+        <v>10.68761394166938</v>
       </c>
       <c r="P3" t="n">
-        <v>297.4719428232626</v>
+        <v>297.7541571510317</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18729,28 +18914,28 @@
         <v>0.196</v>
       </c>
       <c r="I4" t="n">
-        <v>2.974627326508124</v>
+        <v>2.941884143704557</v>
       </c>
       <c r="J4" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K4" t="n">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8398424645928293</v>
+        <v>0.8368006540744504</v>
       </c>
       <c r="M4" t="n">
-        <v>7.909500914504713</v>
+        <v>7.984104051490339</v>
       </c>
       <c r="N4" t="n">
-        <v>94.84014512794197</v>
+        <v>96.26091216642301</v>
       </c>
       <c r="O4" t="n">
-        <v>9.738590510332692</v>
+        <v>9.811264554909474</v>
       </c>
       <c r="P4" t="n">
-        <v>295.3032633327989</v>
+        <v>295.6376623199917</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18807,28 +18992,28 @@
         <v>0.199</v>
       </c>
       <c r="I5" t="n">
-        <v>2.704749829069891</v>
+        <v>2.671836502341587</v>
       </c>
       <c r="J5" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K5" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8376938351784059</v>
+        <v>0.8335906784508608</v>
       </c>
       <c r="M5" t="n">
-        <v>7.258348014711308</v>
+        <v>7.348048882575024</v>
       </c>
       <c r="N5" t="n">
-        <v>79.51865759459176</v>
+        <v>81.12441365460903</v>
       </c>
       <c r="O5" t="n">
-        <v>8.917323454635463</v>
+        <v>9.006909217628932</v>
       </c>
       <c r="P5" t="n">
-        <v>298.2255117771523</v>
+        <v>298.5618317825786</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18885,28 +19070,28 @@
         <v>0.1438</v>
       </c>
       <c r="I6" t="n">
-        <v>1.824369347972155</v>
+        <v>1.799524270188999</v>
       </c>
       <c r="J6" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K6" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7552846403474978</v>
+        <v>0.7505849696488719</v>
       </c>
       <c r="M6" t="n">
-        <v>6.362002578215335</v>
+        <v>6.415995073823748</v>
       </c>
       <c r="N6" t="n">
-        <v>60.49803224923131</v>
+        <v>61.25551387351258</v>
       </c>
       <c r="O6" t="n">
-        <v>7.778048100213273</v>
+        <v>7.826590181778562</v>
       </c>
       <c r="P6" t="n">
-        <v>315.9684197029789</v>
+        <v>316.2222958323805</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18944,7 +19129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G476"/>
+  <dimension ref="A1:G481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36555,6 +36740,191 @@
         </is>
       </c>
     </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>-46.293704680244346,169.92600899589038</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>-46.29428284586445,169.92567621779193</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>-46.29486596611986,169.92536634915055</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>-46.295448516408506,169.92505387850224</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>-46.2960428873062,169.924796022809</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>-46.29370634298231,169.9260166740768</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>-46.294282658133824,169.9256753508919</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>-46.29486561747369,169.92536473917815</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>-46.2954508496797,169.92506465303526</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>-46.29604267275071,169.9247950320376</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>-46.2937082739032,169.92602559068098</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>-46.29428314086969,169.9256775800634</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>-46.294867387523254,169.92537291288446</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-46.29545350478017,169.92507691371193</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>-46.296043209139434,169.92479750896612</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>-46.29370669162086,169.92601828401916</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>-46.294281290381996,169.9256690349062</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>-46.29486521518962,169.92536288151769</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-46.295451546978946,169.92506787301085</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>-46.29604219000082,169.92479280280193</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>-46.29370848844992,169.92602658141482</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>-46.29428123674466,169.9256687872205</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>-46.29486722660969,169.9253721698202</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>-46.295454094802324,169.92507963830695</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>-46.29604674930358,169.92481385669578</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0525/nzd0525.xlsx
+++ b/data/nzd0525/nzd0525.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G481"/>
+  <dimension ref="A1:G483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13421,6 +13421,60 @@
         <v>354.16</v>
       </c>
       <c r="G481" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>371.29</v>
+      </c>
+      <c r="C482" t="n">
+        <v>362.56</v>
+      </c>
+      <c r="D482" t="n">
+        <v>359.21</v>
+      </c>
+      <c r="E482" t="n">
+        <v>354.8</v>
+      </c>
+      <c r="F482" t="n">
+        <v>353.01</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>370.68</v>
+      </c>
+      <c r="C483" t="n">
+        <v>361.38</v>
+      </c>
+      <c r="D483" t="n">
+        <v>359.02</v>
+      </c>
+      <c r="E483" t="n">
+        <v>354.88</v>
+      </c>
+      <c r="F483" t="n">
+        <v>352.51</v>
+      </c>
+      <c r="G483" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13437,7 +13491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B515"/>
+  <dimension ref="A1:B517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18590,6 +18644,26 @@
       </c>
       <c r="B515" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>-1.06</v>
       </c>
     </row>
   </sheetData>
@@ -18758,28 +18832,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.818063380029312</v>
+        <v>2.812296014794136</v>
       </c>
       <c r="J2" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K2" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8300224990020946</v>
+        <v>0.830546948744358</v>
       </c>
       <c r="M2" t="n">
-        <v>7.988807050739294</v>
+        <v>7.983440894828128</v>
       </c>
       <c r="N2" t="n">
-        <v>92.57849168064435</v>
+        <v>92.38624544494515</v>
       </c>
       <c r="O2" t="n">
-        <v>9.621771753717937</v>
+        <v>9.611776393827789</v>
       </c>
       <c r="P2" t="n">
-        <v>302.2462976233838</v>
+        <v>302.3055009725041</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18836,28 +18910,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.957455351410103</v>
+        <v>2.944721612592645</v>
       </c>
       <c r="J3" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K3" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8133962821506957</v>
+        <v>0.8123443449139123</v>
       </c>
       <c r="M3" t="n">
-        <v>8.760377615772089</v>
+        <v>8.783495397655093</v>
       </c>
       <c r="N3" t="n">
-        <v>114.2250917661656</v>
+        <v>114.6859011539428</v>
       </c>
       <c r="O3" t="n">
-        <v>10.68761394166938</v>
+        <v>10.70915034696697</v>
       </c>
       <c r="P3" t="n">
-        <v>297.7541571510317</v>
+        <v>297.8848714664997</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18914,28 +18988,28 @@
         <v>0.196</v>
       </c>
       <c r="I4" t="n">
-        <v>2.941884143704557</v>
+        <v>2.928884488989686</v>
       </c>
       <c r="J4" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K4" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8368006540744504</v>
+        <v>0.8355559451589272</v>
       </c>
       <c r="M4" t="n">
-        <v>7.984104051490339</v>
+        <v>8.015508200545113</v>
       </c>
       <c r="N4" t="n">
-        <v>96.26091216642301</v>
+        <v>96.83578344629112</v>
       </c>
       <c r="O4" t="n">
-        <v>9.811264554909474</v>
+        <v>9.840517437934405</v>
       </c>
       <c r="P4" t="n">
-        <v>295.6376623199917</v>
+        <v>295.7710297638501</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18992,28 +19066,28 @@
         <v>0.199</v>
       </c>
       <c r="I5" t="n">
-        <v>2.671836502341587</v>
+        <v>2.658865529965595</v>
       </c>
       <c r="J5" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K5" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8335906784508608</v>
+        <v>0.831954414880138</v>
       </c>
       <c r="M5" t="n">
-        <v>7.348048882575024</v>
+        <v>7.384710839625759</v>
       </c>
       <c r="N5" t="n">
-        <v>81.12441365460903</v>
+        <v>81.75613887820356</v>
       </c>
       <c r="O5" t="n">
-        <v>9.006909217628932</v>
+        <v>9.041910134379989</v>
       </c>
       <c r="P5" t="n">
-        <v>298.5618317825786</v>
+        <v>298.6949788367268</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19070,28 +19144,28 @@
         <v>0.1438</v>
       </c>
       <c r="I6" t="n">
-        <v>1.799524270188999</v>
+        <v>1.789637148192516</v>
       </c>
       <c r="J6" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K6" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7505849696488719</v>
+        <v>0.7486506612466015</v>
       </c>
       <c r="M6" t="n">
-        <v>6.415995073823748</v>
+        <v>6.437168004133663</v>
       </c>
       <c r="N6" t="n">
-        <v>61.25551387351258</v>
+        <v>61.56424462691404</v>
       </c>
       <c r="O6" t="n">
-        <v>7.826590181778562</v>
+        <v>7.846288589321325</v>
       </c>
       <c r="P6" t="n">
-        <v>316.2222958323805</v>
+        <v>316.3237882322185</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19129,7 +19203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G481"/>
+  <dimension ref="A1:G483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36925,6 +36999,80 @@
         </is>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>-46.293704224332245,169.92600689058128</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>-46.29427793804762,169.92565355455054</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>-46.29486607339561,169.92536684452668</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>-46.29545135924453,169.92506700609434</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>-46.29604366506978,169.9247996143554</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>-46.29370258841198,169.9259993362372</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>-46.29427477344209,169.92563894109662</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>-46.29486556383581,169.9253644914901</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>-46.29545157379814,169.92506799685606</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>-46.296042324098025,169.92479342203407</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
